--- a/data/trans_dic/P25A$otro-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,56</t>
+          <t>6,03; 51,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,72</t>
+          <t>0,0; 26,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 32,64</t>
+          <t>3,52; 34,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,4</t>
+          <t>0,0; 12,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,89</t>
+          <t>0,0; 26,51</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,18</t>
+          <t>0,0; 11,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,99</t>
+          <t>1,29; 11,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 21,66</t>
+          <t>2,49; 20,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,35; 33,5</t>
+          <t>13,99; 34,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 23,81</t>
+          <t>7,76; 23,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,17; 33,16</t>
+          <t>12,5; 34,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 23,69</t>
+          <t>9,82; 23,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,31; 16,14</t>
+          <t>5,55; 15,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 23,54</t>
+          <t>9,18; 24,24</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,04</t>
+          <t>0,0; 7,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,83</t>
+          <t>0,84; 8,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 23,66</t>
+          <t>6,53; 22,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 16,74</t>
+          <t>1,65; 15,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 22,26</t>
+          <t>7,07; 22,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,73</t>
+          <t>1,97; 9,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,19</t>
+          <t>0,82; 5,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 19,22</t>
+          <t>8,29; 19,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,54</t>
+          <t>0,86; 8,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 14,17</t>
+          <t>3,07; 13,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,48</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,85</t>
+          <t>1,17; 10,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 22,58</t>
+          <t>6,74; 21,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,06</t>
+          <t>1,2; 7,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,11</t>
+          <t>1,13; 4,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,57</t>
+          <t>5,96; 14,55</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 8,06</t>
+          <t>1,38; 7,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,57</t>
+          <t>0,67; 5,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 20,54</t>
+          <t>7,58; 20,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 24,21</t>
+          <t>2,04; 23,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,76</t>
+          <t>1,16; 7,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,57</t>
+          <t>0,49; 4,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 17,94</t>
+          <t>8,12; 18,26</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,92; 13,61</t>
+          <t>4,06; 13,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,06</t>
+          <t>0,0; 33,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,93</t>
+          <t>0,0; 20,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,91</t>
+          <t>0,61; 5,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,27</t>
+          <t>3,93; 12,5</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 9,25</t>
+          <t>0,75; 9,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 12,22</t>
+          <t>3,0; 12,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,08</t>
+          <t>0,71; 8,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,35</t>
+          <t>3,0; 12,14</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,85</t>
+          <t>1,29; 3,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,57</t>
+          <t>1,19; 3,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,09</t>
+          <t>7,13; 11,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,29</t>
+          <t>7,57; 15,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,42</t>
+          <t>3,17; 7,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,24</t>
+          <t>9,39; 16,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,47</t>
+          <t>3,45; 6,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,28</t>
+          <t>2,11; 4,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,91</t>
+          <t>8,8; 12,82</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1871</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7808</t>
+          <t>931; 7911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4176</t>
+          <t>0; 5030</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>923; 8726</t>
+          <t>940; 9202</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5185</t>
+          <t>0; 4546</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6718</t>
+          <t>0; 6879</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5988</t>
+          <t>0; 4382</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>922; 7996</t>
+          <t>940; 8082</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1242; 10525</t>
+          <t>1212; 9820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9352; 23473</t>
+          <t>9802; 24144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6054; 19727</t>
+          <t>6433; 19622</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7057; 19221</t>
+          <t>7243; 19905</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10325; 25948</t>
+          <t>10752; 25671</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8259; 25107</t>
+          <t>8628; 23956</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10041; 25083</t>
+          <t>9780; 25828</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6827</t>
+          <t>0; 6571</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>937; 8803</t>
+          <t>947; 9591</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5059; 17585</t>
+          <t>4850; 16555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1980; 11092</t>
+          <t>1096; 10487</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6464</t>
+          <t>0; 5982</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5967; 19571</t>
+          <t>6214; 19445</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2862; 13200</t>
+          <t>2980; 14059</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1989; 12264</t>
+          <t>1941; 12030</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14387; 31179</t>
+          <t>13457; 31761</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1072; 9467</t>
+          <t>1077; 10864</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6336</t>
+          <t>0; 7019</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3330; 15328</t>
+          <t>3326; 14911</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5570</t>
+          <t>0; 5905</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1084; 9939</t>
+          <t>1072; 9601</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6275; 19919</t>
+          <t>5947; 19084</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1966; 13014</t>
+          <t>2209; 12914</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2107; 13371</t>
+          <t>2965; 12820</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11651; 28617</t>
+          <t>11707; 28581</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1690; 10326</t>
+          <t>1773; 10084</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>939; 7816</t>
+          <t>942; 8052</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11285; 27317</t>
+          <t>10080; 26754</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1837</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2105</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1738; 13782</t>
+          <t>1161; 13592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1663; 11301</t>
+          <t>1683; 10198</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>942; 8765</t>
+          <t>936; 7907</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15261; 34075</t>
+          <t>15423; 34681</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6195</t>
+          <t>0; 6828</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4778</t>
+          <t>0; 5500</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4827; 16770</t>
+          <t>5002; 16697</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4748</t>
+          <t>0; 4523</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1814</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5135</t>
+          <t>0; 5315</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>819; 7998</t>
+          <t>831; 7779</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5964</t>
+          <t>0; 5835</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5726; 18275</t>
+          <t>5861; 18624</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5071</t>
+          <t>0; 6357</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1053; 13082</t>
+          <t>1057; 12884</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3405; 13285</t>
+          <t>3266; 13331</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2147</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1693</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 1420</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4973</t>
+          <t>0; 5083</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1070; 11945</t>
+          <t>1056; 11939</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3333; 13732</t>
+          <t>3338; 13498</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8406; 24022</t>
+          <t>8086; 24256</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10634; 29115</t>
+          <t>9690; 27799</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43893; 73216</t>
+          <t>43197; 71994</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18170; 38337</t>
+          <t>18981; 39836</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11097; 28684</t>
+          <t>12242; 29632</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33090; 57877</t>
+          <t>31537; 56648</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30420; 56623</t>
+          <t>30197; 55524</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25667; 51431</t>
+          <t>25339; 49613</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>81630; 121487</t>
+          <t>82874; 120653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$otro-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Edad-trans_dic.xlsx
@@ -688,37 +688,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,97</t>
+          <t>0,0; 43,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 51,23</t>
+          <t>5,99; 49,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,16</t>
+          <t>0,0; 21,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,39</t>
+          <t>0,0; 30,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 34,42</t>
+          <t>3,35; 32,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,62</t>
+          <t>0,0; 15,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,51</t>
+          <t>0,0; 26,5</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,11</t>
+          <t>0,0; 13,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,11</t>
+          <t>0,02; 10,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 20,21</t>
+          <t>2,59; 21,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,99; 34,46</t>
+          <t>12,89; 33,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 23,68</t>
+          <t>7,31; 23,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,5; 34,34</t>
+          <t>11,94; 33,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 23,44</t>
+          <t>8,87; 23,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 15,4</t>
+          <t>5,24; 15,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 24,24</t>
+          <t>9,23; 24,5</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,54</t>
+          <t>0,84; 8,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 22,28</t>
+          <t>6,18; 21,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 15,83</t>
+          <t>2,94; 16,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 22,11</t>
+          <t>7,0; 21,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,3</t>
+          <t>2,02; 9,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,09</t>
+          <t>1,16; 5,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 19,57</t>
+          <t>8,35; 18,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,65</t>
+          <t>0,86; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 13,78</t>
+          <t>3,19; 14,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>0,0; 11,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,48</t>
+          <t>1,15; 10,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 21,63</t>
+          <t>6,35; 21,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,01</t>
+          <t>1,07; 7,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,9</t>
+          <t>0,83; 4,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 14,55</t>
+          <t>5,76; 14,22</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,87</t>
+          <t>1,41; 8,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,74</t>
+          <t>0,67; 5,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 20,12</t>
+          <t>8,25; 20,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 23,88</t>
+          <t>3,22; 24,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,01</t>
+          <t>1,27; 7,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,12</t>
+          <t>0,48; 4,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 18,26</t>
+          <t>8,22; 18,45</t>
         </is>
       </c>
     </row>
@@ -1228,22 +1228,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,06; 13,55</t>
+          <t>3,85; 13,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,4</t>
+          <t>0,0; 39,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,63</t>
+          <t>0,0; 20,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,74</t>
+          <t>0,62; 6,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 12,5</t>
+          <t>3,35; 11,86</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 9,11</t>
+          <t>0,74; 8,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,26</t>
+          <t>3,3; 12,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 8,07</t>
+          <t>0,71; 8,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,14</t>
+          <t>3,03; 12,69</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,88</t>
+          <t>1,31; 3,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,41</t>
+          <t>1,1; 3,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,89</t>
+          <t>7,27; 12,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,89</t>
+          <t>7,47; 15,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,67</t>
+          <t>2,91; 7,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 16,87</t>
+          <t>9,14; 16,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,34</t>
+          <t>3,52; 6,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,13</t>
+          <t>2,07; 4,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,82</t>
+          <t>8,68; 12,7</t>
         </is>
       </c>
     </row>
@@ -1760,37 +1760,37 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4154</t>
+          <t>0; 4117</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>931; 7911</t>
+          <t>925; 7694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5030</t>
+          <t>0; 4150</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4519</t>
+          <t>0; 5011</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>940; 9202</t>
+          <t>895; 8615</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4546</t>
+          <t>0; 5669</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6879</t>
+          <t>0; 6876</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4382</t>
+          <t>0; 5210</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>940; 8082</t>
+          <t>16; 7807</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1212; 9820</t>
+          <t>1259; 10516</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9802; 24144</t>
+          <t>9028; 23780</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6433; 19622</t>
+          <t>6055; 19787</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7243; 19905</t>
+          <t>6924; 19555</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10752; 25671</t>
+          <t>9710; 25380</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8628; 23956</t>
+          <t>8152; 23332</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9780; 25828</t>
+          <t>9839; 26103</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6571</t>
+          <t>0; 6062</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>947; 9591</t>
+          <t>946; 9404</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4850; 16555</t>
+          <t>4594; 16282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1096; 10487</t>
+          <t>1949; 11254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5982</t>
+          <t>0; 6560</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6214; 19445</t>
+          <t>6156; 19207</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2980; 14059</t>
+          <t>3059; 13846</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1941; 12030</t>
+          <t>2745; 12463</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13457; 31761</t>
+          <t>13543; 30710</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1077; 10864</t>
+          <t>1074; 10734</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7019</t>
+          <t>0; 6275</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3326; 14911</t>
+          <t>3455; 15912</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5905</t>
+          <t>0; 6739</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1072; 9601</t>
+          <t>1052; 9955</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5947; 19084</t>
+          <t>5600; 19311</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2209; 12914</t>
+          <t>1964; 14238</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2965; 12820</t>
+          <t>2167; 12697</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11707; 28581</t>
+          <t>11316; 27935</t>
         </is>
       </c>
     </row>
@@ -2402,17 +2402,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1773; 10084</t>
+          <t>1804; 10294</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>942; 8052</t>
+          <t>936; 7839</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10080; 26754</t>
+          <t>10977; 27232</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2427,22 +2427,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1161; 13592</t>
+          <t>1833; 14186</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1683; 10198</t>
+          <t>1845; 10903</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>936; 7907</t>
+          <t>927; 7960</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15423; 34681</t>
+          <t>15614; 35040</t>
         </is>
       </c>
     </row>
@@ -2565,22 +2565,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6828</t>
+          <t>0; 6280</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5500</t>
+          <t>0; 6234</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5002; 16697</t>
+          <t>4750; 16465</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4523</t>
+          <t>0; 5291</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2590,22 +2590,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5315</t>
+          <t>0; 5333</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>831; 7779</t>
+          <t>843; 8156</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5835</t>
+          <t>0; 5485</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5861; 18624</t>
+          <t>4992; 17665</t>
         </is>
       </c>
     </row>
@@ -2728,17 +2728,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6357</t>
+          <t>0; 4173</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1057; 12884</t>
+          <t>1048; 11943</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3266; 13331</t>
+          <t>3585; 13476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 5083</t>
+          <t>0; 4969</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1056; 11939</t>
+          <t>1053; 12654</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3338; 13498</t>
+          <t>3365; 14114</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8086; 24256</t>
+          <t>8171; 23471</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9690; 27799</t>
+          <t>8965; 27330</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43197; 71994</t>
+          <t>44049; 73170</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18981; 39836</t>
+          <t>18728; 38528</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12242; 29632</t>
+          <t>11235; 29119</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31537; 56648</t>
+          <t>30698; 57047</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30197; 55524</t>
+          <t>30810; 55759</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25339; 49613</t>
+          <t>24869; 48291</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>82874; 120653</t>
+          <t>81718; 119585</t>
         </is>
       </c>
     </row>
